--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_20/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.06256119857152531</v>
+        <v>0.07610397324909557</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.264469707222915</v>
+        <v>0.1698480954510102</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.3348983907899943</v>
+        <v>0.4849349951505343</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.4788299098907732</v>
+        <v>0.7045466246051714</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1702665608413736</v>
+        <v>0.1663324103731546</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.4168726744687699</v>
+        <v>0.5195463890705897</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>54.9975457113695</v>
+        <v>25.86834239726274</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3513877286595659</v>
+        <v>0.1250113171153906</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2421204857217588</v>
+        <v>0.2719599907126965</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.800920281084036</v>
+        <v>0.5313283593706454</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-2.326020805439871</v>
+        <v>0.8062583444852058</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3760811427311772</v>
+        <v>0.1473819633564103</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.964918770925734</v>
+        <v>0.885458686184877</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>57.85465675804794</v>
+        <v>47.66388374434697</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.04119966339842795</v>
+        <v>0.1128998461447135</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2013216748335473</v>
+        <v>0.229116049939252</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.2350185527389612</v>
+        <v>0.5356592792336538</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.3481463950771551</v>
+        <v>0.7581946730119645</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1958105840809348</v>
+        <v>0.1567543120232705</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.219284250575122</v>
+        <v>0.7516857672708785</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>58.30380937129392</v>
+        <v>60.33331039687241</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0318780161135892</v>
+        <v>0.1200748730040522</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.239223143715586</v>
+        <v>0.320025607210829</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.1921731578610391</v>
+        <v>0.4812556463669143</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.3009443652917659</v>
+        <v>0.7163642454801135</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1888028755476296</v>
+        <v>0.1812845463841988</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1759344699364849</v>
+        <v>0.691374966853292</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>62.57443029217288</v>
+        <v>67.54791622891587</v>
       </c>
     </row>
     <row r="6">
@@ -636,29 +636,57 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2774252240879158</v>
+        <v>0.2409998383902798</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2281263361618671</v>
+        <v>0.255481311843772</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.16223198699138</v>
+        <v>0.946696980503943</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.67639811067189</v>
+        <v>1.338624632042546</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1576088624794851</v>
+        <v>0.1907813840305966</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.83404722771249</v>
+        <v>1.315452387231552</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>67.84726112684454</v>
+        <v>71.01109011377699</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026年截至07-31</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.6514140644227251</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.3731474791606494</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>2.586036905050782</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>4.250068407983296</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.09642292879037706</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>15.37928166097945</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>53.84949096801673</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H6"/>
+  <autoFilter ref="A1:H7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>